--- a/backend/etl/uploads/budget_2026/activite_raffinage_consolide.xlsx
+++ b/backend/etl/uploads/budget_2026/activite_raffinage_consolide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pfe\etl site\donnne\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7340A095-0AD4-4510-B4EA-B9F15C072B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500BC460-6628-4633-A226-C57503EE585B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
